--- a/docs/dossiers/dossier-valenton-e30680e6.xlsx
+++ b/docs/dossiers/dossier-valenton-e30680e6.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/07/2026</t>
+          <t>Dossier généré le 07/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-valenton-e30680e6.xlsx
+++ b/docs/dossiers/dossier-valenton-e30680e6.xlsx
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>68/100</t>
+          <t>66/100</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">

--- a/docs/dossiers/dossier-valenton-e30680e6.xlsx
+++ b/docs/dossiers/dossier-valenton-e30680e6.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/07/2026</t>
+          <t>Dossier généré le 08/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-valenton-e30680e6.xlsx
+++ b/docs/dossiers/dossier-valenton-e30680e6.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/07/2026</t>
+          <t>Dossier généré le 09/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-valenton-e30680e6.xlsx
+++ b/docs/dossiers/dossier-valenton-e30680e6.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/07/2026</t>
+          <t>Dossier généré le 10/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-valenton-e30680e6.xlsx
+++ b/docs/dossiers/dossier-valenton-e30680e6.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/07/2026</t>
+          <t>Dossier généré le 11/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-valenton-e30680e6.xlsx
+++ b/docs/dossiers/dossier-valenton-e30680e6.xlsx
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>0.0464</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
     <row r="49">
       <c r="A49" s="21" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,64 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +120 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +124 €/mois.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-valenton-e30680e6.xlsx
+++ b/docs/dossiers/dossier-valenton-e30680e6.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/07/2026</t>
+          <t>Dossier généré le 12/07/2026</t>
         </is>
       </c>
     </row>
